--- a/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_word_phrase_translation_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
+++ b/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_word_phrase_translation_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
@@ -512,52 +512,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5280952380952381</v>
+        <v>0.594</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3414633819301872</v>
+        <v>0.5614078964650053</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4032391181860369</v>
+        <v>0.3090102399090284</v>
       </c>
       <c r="D2" t="n">
-        <v>9.460249058814911</v>
+        <v>5.84749441287234</v>
       </c>
       <c r="E2" t="n">
-        <v>26.20813289820232</v>
+        <v>28.26272045596465</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4840476190476191</v>
+        <v>0.4876</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3288588713331326</v>
+        <v>0.5243469967733814</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6562989993603802</v>
+        <v>0.470370095146147</v>
       </c>
       <c r="I2" t="n">
-        <v>10.42512498023114</v>
+        <v>6.55964742854713</v>
       </c>
       <c r="J2" t="n">
-        <v>5.085484742006869</v>
+        <v>6.38057886150519</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9952380952380953</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9838095238095238</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06730116670092584</v>
+        <v>2.220446049250314e-16</v>
       </c>
       <c r="O2" t="n">
-        <v>4.854752967223909</v>
+        <v>-7.213475800929759e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
